--- a/artfynd/A 43710-2025 artfynd.xlsx
+++ b/artfynd/A 43710-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137320763</v>
       </c>
       <c r="B2" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43710-2025 artfynd.xlsx
+++ b/artfynd/A 43710-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 43710-2025 artfynd.xlsx
+++ b/artfynd/A 43710-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137320763</v>
+        <v>137377215</v>
       </c>
       <c r="B2" t="n">
-        <v>57224</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+          <t>Kvarnbo, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801505</v>
+        <v>801640</v>
       </c>
       <c r="R2" t="n">
-        <v>7328900</v>
+        <v>7328976</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Orrhönor</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,24 +775,379 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137377217</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>801750</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7328995</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohål i tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377217</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137320763</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Ljuså, Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>801505</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7328900</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Orrhönor</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137320763</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137377216</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnbo, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>801662</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7328982</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137377216</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43710-2025 artfynd.xlsx
+++ b/artfynd/A 43710-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137377215</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137377217</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137320763</v>
       </c>
       <c r="B4" t="n">
-        <v>57224</v>
+        <v>57227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137377216</v>
       </c>
       <c r="B5" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
